--- a/diseases/d115/1995-1999.xlsx
+++ b/diseases/d115/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>24</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>7</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>16</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>3</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>2</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>10</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>15</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>2</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>3</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>2</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>5</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>4</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>5</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>5</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>2</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>3</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>8</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>7</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>2</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>4</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>4</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>1</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>3</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18056,9 +17924,6 @@
       </c>
       <c r="O90" t="n">
         <v>3</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
